--- a/90_Output/AF_CPG_data_extraction_[작업자이름].xlsx
+++ b/90_Output/AF_CPG_data_extraction_[작업자이름].xlsx
@@ -470,10 +470,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AV4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="30" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="30" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -708,6 +709,11 @@
         </is>
       </c>
       <c r="AU1" s="5" t="inlineStr">
+        <is>
+          <t>analysis_set</t>
+        </is>
+      </c>
+      <c r="AV1" s="5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
